--- a/data/raw/payments_raw.xlsx
+++ b/data/raw/payments_raw.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payments_raw" sheetId="1" r:id="Rb92d5903c9bb4039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payments_raw" sheetId="1" r:id="R5ead1a2722d74792"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -63,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -82,6 +85,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -331,7 +337,7 @@
       <x:c r="B2" s="9" t="n">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="n">
+      <x:c r="C2" s="10" t="n">
         <x:v>46067</x:v>
       </x:c>
       <x:c r="D2" s="9" t="n">
@@ -348,7 +354,7 @@
       <x:c r="B3" s="9" t="n">
         <x:v>1079</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="n">
+      <x:c r="C3" s="10" t="n">
         <x:v>46065</x:v>
       </x:c>
       <x:c r="D3" s="9" t="n">
@@ -365,7 +371,7 @@
       <x:c r="B4" s="9" t="n">
         <x:v>1041</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="n">
+      <x:c r="C4" s="10" t="n">
         <x:v>46121</x:v>
       </x:c>
       <x:c r="D4" s="9" t="n">
@@ -382,7 +388,7 @@
       <x:c r="B5" s="9" t="n">
         <x:v>1126</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="n">
+      <x:c r="C5" s="10" t="n">
         <x:v>46074</x:v>
       </x:c>
       <x:c r="D5" s="9" t="n">
@@ -399,7 +405,7 @@
       <x:c r="B6" s="9" t="n">
         <x:v>1071</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="n">
+      <x:c r="C6" s="10" t="n">
         <x:v>46109</x:v>
       </x:c>
       <x:c r="D6" s="9" t="n">
@@ -416,7 +422,7 @@
       <x:c r="B7" s="9" t="n">
         <x:v>1111</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="n">
+      <x:c r="C7" s="10" t="n">
         <x:v>46070</x:v>
       </x:c>
       <x:c r="D7" s="9" t="n">
@@ -433,7 +439,7 @@
       <x:c r="B8" s="9" t="n">
         <x:v>1076</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="n">
+      <x:c r="C8" s="10" t="n">
         <x:v>46072</x:v>
       </x:c>
       <x:c r="D8" s="9" t="n">
@@ -450,7 +456,7 @@
       <x:c r="B9" s="9" t="n">
         <x:v>1007</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="n">
+      <x:c r="C9" s="10" t="n">
         <x:v>46103</x:v>
       </x:c>
       <x:c r="D9" s="9" t="n">
@@ -467,7 +473,7 @@
       <x:c r="B10" s="9" t="n">
         <x:v>1105</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="n">
+      <x:c r="C10" s="10" t="n">
         <x:v>46070</x:v>
       </x:c>
       <x:c r="D10" s="9" t="n">
@@ -484,7 +490,7 @@
       <x:c r="B11" s="9" t="n">
         <x:v>9999</x:v>
       </x:c>
-      <x:c r="C11" s="9" t="n">
+      <x:c r="C11" s="10" t="n">
         <x:v>46131</x:v>
       </x:c>
       <x:c r="D11" s="9" t="n">
@@ -501,7 +507,7 @@
       <x:c r="B12" s="9" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="C12" s="9" t="n">
+      <x:c r="C12" s="10" t="n">
         <x:v>46075</x:v>
       </x:c>
       <x:c r="D12" s="9" t="n">
@@ -518,7 +524,7 @@
       <x:c r="B13" s="9" t="n">
         <x:v>1119</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="n">
+      <x:c r="C13" s="10" t="n">
         <x:v>46153</x:v>
       </x:c>
       <x:c r="D13" s="9" t="n">
@@ -535,7 +541,7 @@
       <x:c r="B14" s="9" t="n">
         <x:v>1093</x:v>
       </x:c>
-      <x:c r="C14" s="9" t="n">
+      <x:c r="C14" s="10" t="n">
         <x:v>46118</x:v>
       </x:c>
       <x:c r="D14" s="9" t="n">
@@ -552,7 +558,7 @@
       <x:c r="B15" s="9" t="n">
         <x:v>1135</x:v>
       </x:c>
-      <x:c r="C15" s="9" t="n">
+      <x:c r="C15" s="10" t="n">
         <x:v>46156</x:v>
       </x:c>
       <x:c r="D15" s="9" t="n">
@@ -569,7 +575,7 @@
       <x:c r="B16" s="9" t="n">
         <x:v>1147</x:v>
       </x:c>
-      <x:c r="C16" s="9" t="n">
+      <x:c r="C16" s="10" t="n">
         <x:v>46116</x:v>
       </x:c>
       <x:c r="D16" s="9" t="n">
@@ -586,7 +592,7 @@
       <x:c r="B17" s="9" t="n">
         <x:v>1036</x:v>
       </x:c>
-      <x:c r="C17" s="9" t="n">
+      <x:c r="C17" s="10" t="n">
         <x:v>46047</x:v>
       </x:c>
       <x:c r="D17" s="9" t="n">
@@ -603,7 +609,7 @@
       <x:c r="B18" s="9" t="n">
         <x:v>1021</x:v>
       </x:c>
-      <x:c r="C18" s="9" t="n">
+      <x:c r="C18" s="10" t="n">
         <x:v>46179</x:v>
       </x:c>
       <x:c r="D18" s="9" t="n">
@@ -620,7 +626,7 @@
       <x:c r="B19" s="9" t="n">
         <x:v>1141</x:v>
       </x:c>
-      <x:c r="C19" s="9" t="n">
+      <x:c r="C19" s="10" t="n">
         <x:v>46183</x:v>
       </x:c>
       <x:c r="D19" s="9" t="n">
@@ -637,7 +643,7 @@
       <x:c r="B20" s="9" t="n">
         <x:v>1093</x:v>
       </x:c>
-      <x:c r="C20" s="9" t="n">
+      <x:c r="C20" s="10" t="n">
         <x:v>46130</x:v>
       </x:c>
       <x:c r="D20" s="9" t="n">
@@ -654,7 +660,7 @@
       <x:c r="B21" s="9" t="n">
         <x:v>1160</x:v>
       </x:c>
-      <x:c r="C21" s="9" t="n">
+      <x:c r="C21" s="10" t="n">
         <x:v>46074</x:v>
       </x:c>
       <x:c r="D21" s="9" t="n">
@@ -671,7 +677,7 @@
       <x:c r="B22" s="9" t="n">
         <x:v>1009</x:v>
       </x:c>
-      <x:c r="C22" s="9" t="n">
+      <x:c r="C22" s="10" t="n">
         <x:v>46120</x:v>
       </x:c>
       <x:c r="D22" s="9" t="n">
@@ -688,7 +694,7 @@
       <x:c r="B23" s="9" t="n">
         <x:v>1104</x:v>
       </x:c>
-      <x:c r="C23" s="9" t="n">
+      <x:c r="C23" s="10" t="n">
         <x:v>46062</x:v>
       </x:c>
       <x:c r="D23" s="9" t="n">
@@ -705,7 +711,7 @@
       <x:c r="B24" s="9" t="n">
         <x:v>1144</x:v>
       </x:c>
-      <x:c r="C24" s="9" t="n">
+      <x:c r="C24" s="10" t="n">
         <x:v>46175</x:v>
       </x:c>
       <x:c r="D24" s="9" t="n">
@@ -722,7 +728,7 @@
       <x:c r="B25" s="9" t="n">
         <x:v>1062</x:v>
       </x:c>
-      <x:c r="C25" s="9" t="n">
+      <x:c r="C25" s="10" t="n">
         <x:v>46172</x:v>
       </x:c>
       <x:c r="D25" s="9" t="n">
@@ -739,7 +745,7 @@
       <x:c r="B26" s="9" t="n">
         <x:v>1149</x:v>
       </x:c>
-      <x:c r="C26" s="9" t="n">
+      <x:c r="C26" s="10" t="n">
         <x:v>46083</x:v>
       </x:c>
       <x:c r="D26" s="9" t="n">
@@ -756,7 +762,7 @@
       <x:c r="B27" s="9" t="n">
         <x:v>1022</x:v>
       </x:c>
-      <x:c r="C27" s="9" t="n">
+      <x:c r="C27" s="10" t="n">
         <x:v>46054</x:v>
       </x:c>
       <x:c r="D27" s="9" t="n">
@@ -773,7 +779,7 @@
       <x:c r="B28" s="9" t="n">
         <x:v>1093</x:v>
       </x:c>
-      <x:c r="C28" s="9" t="n">
+      <x:c r="C28" s="10" t="n">
         <x:v>46120</x:v>
       </x:c>
       <x:c r="D28" s="9" t="n">
@@ -788,7 +794,7 @@
       <x:c r="B29" s="9" t="n">
         <x:v>1156</x:v>
       </x:c>
-      <x:c r="C29" s="9" t="n">
+      <x:c r="C29" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="D29" s="9" t="n">
@@ -805,7 +811,7 @@
       <x:c r="B30" s="9" t="n">
         <x:v>1072</x:v>
       </x:c>
-      <x:c r="C30" s="9" t="n">
+      <x:c r="C30" s="10" t="n">
         <x:v>46124</x:v>
       </x:c>
       <x:c r="D30" s="9" t="n">
@@ -822,7 +828,7 @@
       <x:c r="B31" s="9" t="n">
         <x:v>1148</x:v>
       </x:c>
-      <x:c r="C31" s="9" t="n">
+      <x:c r="C31" s="10" t="n">
         <x:v>46051</x:v>
       </x:c>
       <x:c r="D31" s="9" t="n">
@@ -839,7 +845,7 @@
       <x:c r="B32" s="9" t="n">
         <x:v>1134</x:v>
       </x:c>
-      <x:c r="C32" s="9" t="n">
+      <x:c r="C32" s="10" t="n">
         <x:v>46086</x:v>
       </x:c>
       <x:c r="D32" s="9" t="n">
@@ -856,7 +862,7 @@
       <x:c r="B33" s="9" t="n">
         <x:v>1153</x:v>
       </x:c>
-      <x:c r="C33" s="9" t="n">
+      <x:c r="C33" s="10" t="n">
         <x:v>46152</x:v>
       </x:c>
       <x:c r="D33" s="9" t="n">
@@ -873,7 +879,7 @@
       <x:c r="B34" s="9" t="n">
         <x:v>1134</x:v>
       </x:c>
-      <x:c r="C34" s="9" t="n">
+      <x:c r="C34" s="10" t="n">
         <x:v>46080</x:v>
       </x:c>
       <x:c r="D34" s="9" t="n">
@@ -890,7 +896,7 @@
       <x:c r="B35" s="9" t="n">
         <x:v>1041</x:v>
       </x:c>
-      <x:c r="C35" s="9" t="n">
+      <x:c r="C35" s="10" t="n">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="D35" s="9" t="n">
@@ -907,7 +913,7 @@
       <x:c r="B36" s="9" t="n">
         <x:v>1138</x:v>
       </x:c>
-      <x:c r="C36" s="9" t="n">
+      <x:c r="C36" s="10" t="n">
         <x:v>46144</x:v>
       </x:c>
       <x:c r="D36" s="9" t="n">
@@ -924,7 +930,7 @@
       <x:c r="B37" s="9" t="n">
         <x:v>1145</x:v>
       </x:c>
-      <x:c r="C37" s="9" t="n">
+      <x:c r="C37" s="10" t="n">
         <x:v>46121</x:v>
       </x:c>
       <x:c r="D37" s="9" t="n">
@@ -941,7 +947,7 @@
       <x:c r="B38" s="9" t="n">
         <x:v>1041</x:v>
       </x:c>
-      <x:c r="C38" s="9" t="n">
+      <x:c r="C38" s="10" t="n">
         <x:v>46136</x:v>
       </x:c>
       <x:c r="D38" s="9" t="n">
@@ -958,7 +964,7 @@
       <x:c r="B39" s="9" t="n">
         <x:v>1021</x:v>
       </x:c>
-      <x:c r="C39" s="9" t="n">
+      <x:c r="C39" s="10" t="n">
         <x:v>46160</x:v>
       </x:c>
       <x:c r="D39" s="9" t="n">
@@ -975,7 +981,7 @@
       <x:c r="B40" s="9" t="n">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="C40" s="9" t="n">
+      <x:c r="C40" s="10" t="n">
         <x:v>46040</x:v>
       </x:c>
       <x:c r="D40" s="9" t="n">
@@ -992,7 +998,7 @@
       <x:c r="B41" s="9" t="n">
         <x:v>1057</x:v>
       </x:c>
-      <x:c r="C41" s="9" t="n">
+      <x:c r="C41" s="10" t="n">
         <x:v>46179</x:v>
       </x:c>
       <x:c r="D41" s="9" t="n">
@@ -1009,7 +1015,7 @@
       <x:c r="B42" s="9" t="n">
         <x:v>1138</x:v>
       </x:c>
-      <x:c r="C42" s="9" t="n">
+      <x:c r="C42" s="10" t="n">
         <x:v>46156</x:v>
       </x:c>
       <x:c r="D42" s="9" t="n">
@@ -1026,7 +1032,7 @@
       <x:c r="B43" s="9" t="n">
         <x:v>1119</x:v>
       </x:c>
-      <x:c r="C43" s="9" t="n">
+      <x:c r="C43" s="10" t="n">
         <x:v>46153</x:v>
       </x:c>
       <x:c r="D43" s="9" t="n">
@@ -1043,7 +1049,7 @@
       <x:c r="B44" s="9" t="n">
         <x:v>1047</x:v>
       </x:c>
-      <x:c r="C44" s="9" t="n">
+      <x:c r="C44" s="10" t="n">
         <x:v>46164</x:v>
       </x:c>
       <x:c r="D44" s="9" t="n">
@@ -1060,7 +1066,7 @@
       <x:c r="B45" s="9" t="n">
         <x:v>1044</x:v>
       </x:c>
-      <x:c r="C45" s="9" t="n">
+      <x:c r="C45" s="10" t="n">
         <x:v>46175</x:v>
       </x:c>
       <x:c r="D45" s="9" t="n">
@@ -1077,7 +1083,7 @@
       <x:c r="B46" s="9" t="n">
         <x:v>1032</x:v>
       </x:c>
-      <x:c r="C46" s="9" t="n">
+      <x:c r="C46" s="10" t="n">
         <x:v>46074</x:v>
       </x:c>
       <x:c r="D46" s="9" t="n">
@@ -1094,7 +1100,7 @@
       <x:c r="B47" s="9" t="n">
         <x:v>1096</x:v>
       </x:c>
-      <x:c r="C47" s="9" t="n">
+      <x:c r="C47" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="D47" s="9" t="n">
@@ -1111,7 +1117,7 @@
       <x:c r="B48" s="9" t="n">
         <x:v>1064</x:v>
       </x:c>
-      <x:c r="C48" s="9" t="n">
+      <x:c r="C48" s="10" t="n">
         <x:v>46142</x:v>
       </x:c>
       <x:c r="D48" s="9" t="n">
@@ -1128,7 +1134,7 @@
       <x:c r="B49" s="9" t="n">
         <x:v>1001</x:v>
       </x:c>
-      <x:c r="C49" s="9" t="n">
+      <x:c r="C49" s="10" t="n">
         <x:v>46116</x:v>
       </x:c>
       <x:c r="D49" s="9" t="n">
@@ -1145,7 +1151,7 @@
       <x:c r="B50" s="9" t="n">
         <x:v>1134</x:v>
       </x:c>
-      <x:c r="C50" s="9" t="n">
+      <x:c r="C50" s="10" t="n">
         <x:v>46070</x:v>
       </x:c>
       <x:c r="D50" s="9" t="n">
@@ -1162,7 +1168,7 @@
       <x:c r="B51" s="9" t="n">
         <x:v>1007</x:v>
       </x:c>
-      <x:c r="C51" s="9" t="n">
+      <x:c r="C51" s="10" t="n">
         <x:v>46119</x:v>
       </x:c>
       <x:c r="D51" s="9" t="n">
@@ -1179,7 +1185,7 @@
       <x:c r="B52" s="9" t="n">
         <x:v>1042</x:v>
       </x:c>
-      <x:c r="C52" s="9" t="n">
+      <x:c r="C52" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="D52" s="9" t="n">
@@ -1196,7 +1202,7 @@
       <x:c r="B53" s="9" t="n">
         <x:v>1106</x:v>
       </x:c>
-      <x:c r="C53" s="9" t="n">
+      <x:c r="C53" s="10" t="n">
         <x:v>46127</x:v>
       </x:c>
       <x:c r="D53" s="9" t="n">
@@ -1213,7 +1219,7 @@
       <x:c r="B54" s="9" t="n">
         <x:v>1153</x:v>
       </x:c>
-      <x:c r="C54" s="9" t="n">
+      <x:c r="C54" s="10" t="n">
         <x:v>46134</x:v>
       </x:c>
       <x:c r="D54" s="9" t="n">
@@ -1230,7 +1236,7 @@
       <x:c r="B55" s="9" t="n">
         <x:v>1081</x:v>
       </x:c>
-      <x:c r="C55" s="9" t="n">
+      <x:c r="C55" s="10" t="n">
         <x:v>46079</x:v>
       </x:c>
       <x:c r="D55" s="9" t="n">
@@ -1247,7 +1253,7 @@
       <x:c r="B56" s="9" t="n">
         <x:v>1121</x:v>
       </x:c>
-      <x:c r="C56" s="9" t="n">
+      <x:c r="C56" s="10" t="n">
         <x:v>46141</x:v>
       </x:c>
       <x:c r="D56" s="9" t="n">
@@ -1264,7 +1270,7 @@
       <x:c r="B57" s="9" t="n">
         <x:v>1090</x:v>
       </x:c>
-      <x:c r="C57" s="9" t="n">
+      <x:c r="C57" s="10" t="n">
         <x:v>46139</x:v>
       </x:c>
       <x:c r="D57" s="9" t="n">
@@ -1281,7 +1287,7 @@
       <x:c r="B58" s="9" t="n">
         <x:v>1025</x:v>
       </x:c>
-      <x:c r="C58" s="9" t="n">
+      <x:c r="C58" s="10" t="n">
         <x:v>46175</x:v>
       </x:c>
       <x:c r="D58" s="9" t="n">
@@ -1298,7 +1304,7 @@
       <x:c r="B59" s="9" t="n">
         <x:v>1069</x:v>
       </x:c>
-      <x:c r="C59" s="9" t="n">
+      <x:c r="C59" s="10" t="n">
         <x:v>46180</x:v>
       </x:c>
       <x:c r="D59" s="9" t="n">
@@ -1315,7 +1321,7 @@
       <x:c r="B60" s="9" t="n">
         <x:v>1013</x:v>
       </x:c>
-      <x:c r="C60" s="9" t="n">
+      <x:c r="C60" s="10" t="n">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="D60" s="9" t="n">
@@ -1332,7 +1338,7 @@
       <x:c r="B61" s="9" t="n">
         <x:v>1122</x:v>
       </x:c>
-      <x:c r="C61" s="9" t="n">
+      <x:c r="C61" s="10" t="n">
         <x:v>46091</x:v>
       </x:c>
       <x:c r="D61" s="9" t="n">
@@ -1349,7 +1355,7 @@
       <x:c r="B62" s="9" t="n">
         <x:v>1045</x:v>
       </x:c>
-      <x:c r="C62" s="9" t="n">
+      <x:c r="C62" s="10" t="n">
         <x:v>46131</x:v>
       </x:c>
       <x:c r="D62" s="9" t="n">
@@ -1366,7 +1372,7 @@
       <x:c r="B63" s="9" t="n">
         <x:v>1015</x:v>
       </x:c>
-      <x:c r="C63" s="9" t="n">
+      <x:c r="C63" s="10" t="n">
         <x:v>46095</x:v>
       </x:c>
       <x:c r="D63" s="9" t="n">
@@ -1383,7 +1389,7 @@
       <x:c r="B64" s="9" t="n">
         <x:v>1110</x:v>
       </x:c>
-      <x:c r="C64" s="9" t="n">
+      <x:c r="C64" s="10" t="n">
         <x:v>46110</x:v>
       </x:c>
       <x:c r="D64" s="9" t="n">
@@ -1400,7 +1406,7 @@
       <x:c r="B65" s="9" t="n">
         <x:v>1083</x:v>
       </x:c>
-      <x:c r="C65" s="9" t="n">
+      <x:c r="C65" s="10" t="n">
         <x:v>46150</x:v>
       </x:c>
       <x:c r="D65" s="9" t="n">
@@ -1417,7 +1423,7 @@
       <x:c r="B66" s="9" t="n">
         <x:v>1081</x:v>
       </x:c>
-      <x:c r="C66" s="9" t="n">
+      <x:c r="C66" s="10" t="n">
         <x:v>46075</x:v>
       </x:c>
       <x:c r="D66" s="9" t="n">
@@ -1434,7 +1440,7 @@
       <x:c r="B67" s="9" t="n">
         <x:v>1147</x:v>
       </x:c>
-      <x:c r="C67" s="9" t="n">
+      <x:c r="C67" s="10" t="n">
         <x:v>46114</x:v>
       </x:c>
       <x:c r="D67" s="9" t="n">
@@ -1451,7 +1457,7 @@
       <x:c r="B68" s="9" t="n">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="C68" s="9" t="n">
+      <x:c r="C68" s="10" t="n">
         <x:v>46053</x:v>
       </x:c>
       <x:c r="D68" s="9" t="n">
@@ -1468,7 +1474,7 @@
       <x:c r="B69" s="9" t="n">
         <x:v>1116</x:v>
       </x:c>
-      <x:c r="C69" s="9" t="n">
+      <x:c r="C69" s="10" t="n">
         <x:v>46066</x:v>
       </x:c>
       <x:c r="D69" s="9" t="n">
@@ -1485,7 +1491,7 @@
       <x:c r="B70" s="9" t="n">
         <x:v>1066</x:v>
       </x:c>
-      <x:c r="C70" s="9" t="n">
+      <x:c r="C70" s="10" t="n">
         <x:v>46173</x:v>
       </x:c>
       <x:c r="D70" s="9" t="n">
@@ -1502,7 +1508,7 @@
       <x:c r="B71" s="9" t="n">
         <x:v>1060</x:v>
       </x:c>
-      <x:c r="C71" s="9" t="n">
+      <x:c r="C71" s="10" t="n">
         <x:v>46048</x:v>
       </x:c>
       <x:c r="D71" s="9" t="n">
@@ -1519,7 +1525,7 @@
       <x:c r="B72" s="9" t="n">
         <x:v>1151</x:v>
       </x:c>
-      <x:c r="C72" s="9" t="n">
+      <x:c r="C72" s="10" t="n">
         <x:v>46182</x:v>
       </x:c>
       <x:c r="D72" s="9" t="n">
@@ -1536,7 +1542,7 @@
       <x:c r="B73" s="9" t="n">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="C73" s="9" t="n">
+      <x:c r="C73" s="10" t="n">
         <x:v>46049</x:v>
       </x:c>
       <x:c r="D73" s="9" t="n">
@@ -1553,7 +1559,7 @@
       <x:c r="B74" s="9" t="n">
         <x:v>1130</x:v>
       </x:c>
-      <x:c r="C74" s="9" t="n">
+      <x:c r="C74" s="10" t="n">
         <x:v>46164</x:v>
       </x:c>
       <x:c r="D74" s="9" t="n">
@@ -1570,7 +1576,7 @@
       <x:c r="B75" s="9" t="n">
         <x:v>1002</x:v>
       </x:c>
-      <x:c r="C75" s="9" t="n">
+      <x:c r="C75" s="10" t="n">
         <x:v>46163</x:v>
       </x:c>
       <x:c r="D75" s="9" t="n">
@@ -1587,7 +1593,7 @@
       <x:c r="B76" s="9" t="n">
         <x:v>1016</x:v>
       </x:c>
-      <x:c r="C76" s="9" t="n">
+      <x:c r="C76" s="10" t="n">
         <x:v>46147</x:v>
       </x:c>
       <x:c r="D76" s="9" t="n">
@@ -1604,7 +1610,7 @@
       <x:c r="B77" s="9" t="n">
         <x:v>1016</x:v>
       </x:c>
-      <x:c r="C77" s="9" t="n">
+      <x:c r="C77" s="10" t="n">
         <x:v>46140</x:v>
       </x:c>
       <x:c r="D77" s="9" t="n">
@@ -1621,7 +1627,7 @@
       <x:c r="B78" s="9" t="n">
         <x:v>1136</x:v>
       </x:c>
-      <x:c r="C78" s="9" t="n">
+      <x:c r="C78" s="10" t="n">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="D78" s="9" t="n">
@@ -1638,7 +1644,7 @@
       <x:c r="B79" s="9" t="n">
         <x:v>1062</x:v>
       </x:c>
-      <x:c r="C79" s="9" t="n">
+      <x:c r="C79" s="10" t="n">
         <x:v>46178</x:v>
       </x:c>
       <x:c r="D79" s="9" t="n">
@@ -1655,7 +1661,7 @@
       <x:c r="B80" s="9" t="n">
         <x:v>1112</x:v>
       </x:c>
-      <x:c r="C80" s="9" t="n">
+      <x:c r="C80" s="10" t="n">
         <x:v>46117</x:v>
       </x:c>
       <x:c r="D80" s="9" t="n">
@@ -1672,7 +1678,7 @@
       <x:c r="B81" s="9" t="n">
         <x:v>1160</x:v>
       </x:c>
-      <x:c r="C81" s="9" t="n">
+      <x:c r="C81" s="10" t="n">
         <x:v>46085</x:v>
       </x:c>
       <x:c r="D81" s="9" t="n">
@@ -1689,7 +1695,7 @@
       <x:c r="B82" s="9" t="n">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="C82" s="9" t="n">
+      <x:c r="C82" s="10" t="n">
         <x:v>46181</x:v>
       </x:c>
       <x:c r="D82" s="9" t="n">
@@ -1706,7 +1712,7 @@
       <x:c r="B83" s="9" t="n">
         <x:v>1069</x:v>
       </x:c>
-      <x:c r="C83" s="9" t="n">
+      <x:c r="C83" s="10" t="n">
         <x:v>46168</x:v>
       </x:c>
       <x:c r="D83" s="9" t="n">
@@ -1723,7 +1729,7 @@
       <x:c r="B84" s="9" t="n">
         <x:v>1088</x:v>
       </x:c>
-      <x:c r="C84" s="9" t="n">
+      <x:c r="C84" s="10" t="n">
         <x:v>46132</x:v>
       </x:c>
       <x:c r="D84" s="9" t="n">
@@ -1740,7 +1746,7 @@
       <x:c r="B85" s="9" t="n">
         <x:v>1067</x:v>
       </x:c>
-      <x:c r="C85" s="9" t="n">
+      <x:c r="C85" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="D85" s="9" t="n">
@@ -1757,7 +1763,7 @@
       <x:c r="B86" s="9" t="n">
         <x:v>1138</x:v>
       </x:c>
-      <x:c r="C86" s="9" t="n">
+      <x:c r="C86" s="10" t="n">
         <x:v>46142</x:v>
       </x:c>
       <x:c r="D86" s="9" t="n">
@@ -1774,7 +1780,7 @@
       <x:c r="B87" s="9" t="n">
         <x:v>1079</x:v>
       </x:c>
-      <x:c r="C87" s="9" t="n">
+      <x:c r="C87" s="10" t="n">
         <x:v>46065</x:v>
       </x:c>
       <x:c r="D87" s="9" t="n">
@@ -1791,7 +1797,7 @@
       <x:c r="B88" s="9" t="n">
         <x:v>1130</x:v>
       </x:c>
-      <x:c r="C88" s="9" t="n">
+      <x:c r="C88" s="10" t="n">
         <x:v>46171</x:v>
       </x:c>
       <x:c r="D88" s="9" t="n">
@@ -1808,7 +1814,7 @@
       <x:c r="B89" s="9" t="n">
         <x:v>1038</x:v>
       </x:c>
-      <x:c r="C89" s="9" t="n">
+      <x:c r="C89" s="10" t="n">
         <x:v>46174</x:v>
       </x:c>
       <x:c r="D89" s="9" t="n">
@@ -1825,7 +1831,7 @@
       <x:c r="B90" s="9" t="n">
         <x:v>1054</x:v>
       </x:c>
-      <x:c r="C90" s="9" t="n">
+      <x:c r="C90" s="10" t="n">
         <x:v>46046</x:v>
       </x:c>
       <x:c r="D90" s="9" t="n">
@@ -1842,7 +1848,7 @@
       <x:c r="B91" s="9" t="n">
         <x:v>1128</x:v>
       </x:c>
-      <x:c r="C91" s="9" t="n">
+      <x:c r="C91" s="10" t="n">
         <x:v>46147</x:v>
       </x:c>
       <x:c r="D91" s="9" t="n">
@@ -1859,7 +1865,7 @@
       <x:c r="B92" s="9" t="n">
         <x:v>1097</x:v>
       </x:c>
-      <x:c r="C92" s="9" t="n">
+      <x:c r="C92" s="10" t="n">
         <x:v>46112</x:v>
       </x:c>
       <x:c r="D92" s="9" t="n">
@@ -1876,7 +1882,7 @@
       <x:c r="B93" s="9" t="n">
         <x:v>1004</x:v>
       </x:c>
-      <x:c r="C93" s="9" t="n">
+      <x:c r="C93" s="10" t="n">
         <x:v>46048</x:v>
       </x:c>
       <x:c r="D93" s="9" t="n">
@@ -1893,7 +1899,7 @@
       <x:c r="B94" s="9" t="n">
         <x:v>1113</x:v>
       </x:c>
-      <x:c r="C94" s="9" t="n">
+      <x:c r="C94" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="D94" s="9" t="n">
@@ -1910,7 +1916,7 @@
       <x:c r="B95" s="9" t="n">
         <x:v>1157</x:v>
       </x:c>
-      <x:c r="C95" s="9" t="n">
+      <x:c r="C95" s="10" t="n">
         <x:v>46097</x:v>
       </x:c>
       <x:c r="D95" s="9" t="n">
@@ -1927,7 +1933,7 @@
       <x:c r="B96" s="9" t="n">
         <x:v>1114</x:v>
       </x:c>
-      <x:c r="C96" s="9" t="n">
+      <x:c r="C96" s="10" t="n">
         <x:v>46080</x:v>
       </x:c>
       <x:c r="D96" s="9" t="n">
@@ -1944,7 +1950,7 @@
       <x:c r="B97" s="9" t="n">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="C97" s="9" t="n">
+      <x:c r="C97" s="10" t="n">
         <x:v>46041</x:v>
       </x:c>
       <x:c r="D97" s="9" t="n">
@@ -1961,7 +1967,7 @@
       <x:c r="B98" s="9" t="n">
         <x:v>1013</x:v>
       </x:c>
-      <x:c r="C98" s="9" t="n">
+      <x:c r="C98" s="10" t="n">
         <x:v>46072</x:v>
       </x:c>
       <x:c r="D98" s="9" t="n">
@@ -1978,7 +1984,7 @@
       <x:c r="B99" s="9" t="n">
         <x:v>1081</x:v>
       </x:c>
-      <x:c r="C99" s="9" t="n">
+      <x:c r="C99" s="10" t="n">
         <x:v>46069</x:v>
       </x:c>
       <x:c r="D99" s="9" t="n">
@@ -1995,7 +2001,7 @@
       <x:c r="B100" s="9" t="n">
         <x:v>1137</x:v>
       </x:c>
-      <x:c r="C100" s="9" t="n">
+      <x:c r="C100" s="10" t="n">
         <x:v>46044</x:v>
       </x:c>
       <x:c r="D100" s="9" t="n">
@@ -2012,7 +2018,7 @@
       <x:c r="B101" s="9" t="n">
         <x:v>1007</x:v>
       </x:c>
-      <x:c r="C101" s="9" t="n">
+      <x:c r="C101" s="10" t="n">
         <x:v>46143</x:v>
       </x:c>
       <x:c r="D101" s="9" t="n">
@@ -2029,7 +2035,7 @@
       <x:c r="B102" s="9" t="n">
         <x:v>1115</x:v>
       </x:c>
-      <x:c r="C102" s="9" t="n">
+      <x:c r="C102" s="10" t="n">
         <x:v>46166</x:v>
       </x:c>
       <x:c r="D102" s="9" t="n">
@@ -2046,7 +2052,7 @@
       <x:c r="B103" s="9" t="n">
         <x:v>1060</x:v>
       </x:c>
-      <x:c r="C103" s="9" t="n">
+      <x:c r="C103" s="10" t="n">
         <x:v>46054</x:v>
       </x:c>
       <x:c r="D103" s="9" t="n">
@@ -2063,7 +2069,7 @@
       <x:c r="B104" s="9" t="n">
         <x:v>1014</x:v>
       </x:c>
-      <x:c r="C104" s="9" t="n">
+      <x:c r="C104" s="10" t="n">
         <x:v>46158</x:v>
       </x:c>
       <x:c r="D104" s="9" t="n">
@@ -2080,7 +2086,7 @@
       <x:c r="B105" s="9" t="n">
         <x:v>1041</x:v>
       </x:c>
-      <x:c r="C105" s="9" t="n">
+      <x:c r="C105" s="10" t="n">
         <x:v>46122</x:v>
       </x:c>
       <x:c r="D105" s="9" t="n">
@@ -2097,7 +2103,7 @@
       <x:c r="B106" s="9" t="n">
         <x:v>1158</x:v>
       </x:c>
-      <x:c r="C106" s="9" t="n">
+      <x:c r="C106" s="10" t="n">
         <x:v>46069</x:v>
       </x:c>
       <x:c r="D106" s="9" t="n">
@@ -2114,7 +2120,7 @@
       <x:c r="B107" s="9" t="n">
         <x:v>1092</x:v>
       </x:c>
-      <x:c r="C107" s="9" t="n">
+      <x:c r="C107" s="10" t="n">
         <x:v>46126</x:v>
       </x:c>
       <x:c r="D107" s="9" t="n">
@@ -2131,7 +2137,7 @@
       <x:c r="B108" s="9" t="n">
         <x:v>1101</x:v>
       </x:c>
-      <x:c r="C108" s="9" t="n">
+      <x:c r="C108" s="10" t="n">
         <x:v>46158</x:v>
       </x:c>
       <x:c r="D108" s="9" t="n">
@@ -2148,7 +2154,7 @@
       <x:c r="B109" s="9" t="n">
         <x:v>1153</x:v>
       </x:c>
-      <x:c r="C109" s="9" t="n">
+      <x:c r="C109" s="10" t="n">
         <x:v>46141</x:v>
       </x:c>
       <x:c r="D109" s="9" t="n">
@@ -2165,7 +2171,7 @@
       <x:c r="B110" s="9" t="n">
         <x:v>1067</x:v>
       </x:c>
-      <x:c r="C110" s="9" t="n">
+      <x:c r="C110" s="10" t="n">
         <x:v>46074</x:v>
       </x:c>
       <x:c r="D110" s="9" t="n">
@@ -2182,7 +2188,7 @@
       <x:c r="B111" s="9" t="n">
         <x:v>1149</x:v>
       </x:c>
-      <x:c r="C111" s="9" t="n">
+      <x:c r="C111" s="10" t="n">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="D111" s="9" t="n">
@@ -2199,7 +2205,7 @@
       <x:c r="B112" s="9" t="n">
         <x:v>1079</x:v>
       </x:c>
-      <x:c r="C112" s="9" t="n">
+      <x:c r="C112" s="10" t="n">
         <x:v>46073</x:v>
       </x:c>
       <x:c r="D112" s="9" t="n">
@@ -2216,7 +2222,7 @@
       <x:c r="B113" s="9" t="n">
         <x:v>1152</x:v>
       </x:c>
-      <x:c r="C113" s="9" t="n">
+      <x:c r="C113" s="10" t="n">
         <x:v>46108</x:v>
       </x:c>
       <x:c r="D113" s="9" t="n">
@@ -2233,7 +2239,7 @@
       <x:c r="B114" s="9" t="n">
         <x:v>1048</x:v>
       </x:c>
-      <x:c r="C114" s="9" t="n">
+      <x:c r="C114" s="10" t="n">
         <x:v>46112</x:v>
       </x:c>
       <x:c r="D114" s="9" t="n">
@@ -2250,7 +2256,7 @@
       <x:c r="B115" s="9" t="n">
         <x:v>1158</x:v>
       </x:c>
-      <x:c r="C115" s="9" t="n">
+      <x:c r="C115" s="10" t="n">
         <x:v>46071</x:v>
       </x:c>
       <x:c r="D115" s="9" t="n">
@@ -2267,7 +2273,7 @@
       <x:c r="B116" s="9" t="n">
         <x:v>1122</x:v>
       </x:c>
-      <x:c r="C116" s="9" t="n">
+      <x:c r="C116" s="10" t="n">
         <x:v>46091</x:v>
       </x:c>
       <x:c r="D116" s="9" t="n">
@@ -2284,7 +2290,7 @@
       <x:c r="B117" s="9" t="n">
         <x:v>1154</x:v>
       </x:c>
-      <x:c r="C117" s="9" t="n">
+      <x:c r="C117" s="10" t="n">
         <x:v>46083</x:v>
       </x:c>
       <x:c r="D117" s="9" t="n">
@@ -2301,7 +2307,7 @@
       <x:c r="B118" s="9" t="n">
         <x:v>1115</x:v>
       </x:c>
-      <x:c r="C118" s="9" t="n">
+      <x:c r="C118" s="10" t="n">
         <x:v>46157</x:v>
       </x:c>
       <x:c r="D118" s="9" t="n">
@@ -2318,7 +2324,7 @@
       <x:c r="B119" s="9" t="n">
         <x:v>1151</x:v>
       </x:c>
-      <x:c r="C119" s="9" t="n">
+      <x:c r="C119" s="10" t="n">
         <x:v>46180</x:v>
       </x:c>
       <x:c r="D119" s="9" t="n">
@@ -2335,7 +2341,7 @@
       <x:c r="B120" s="9" t="n">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="C120" s="9" t="n">
+      <x:c r="C120" s="10" t="n">
         <x:v>46165</x:v>
       </x:c>
       <x:c r="D120" s="9" t="n">
@@ -2352,7 +2358,7 @@
       <x:c r="B121" s="9" t="n">
         <x:v>1144</x:v>
       </x:c>
-      <x:c r="C121" s="9" t="n">
+      <x:c r="C121" s="10" t="n">
         <x:v>46176</x:v>
       </x:c>
       <x:c r="D121" s="9" t="n">
@@ -2365,7 +2371,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ae504fc6384a7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05e2bcf926de4944"/>
   </x:tableParts>
 </x:worksheet>
 </file>